--- a/data/trans_bre/P1002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 5,3</t>
+          <t>-3,84; 5,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 16,72</t>
+          <t>5,32; 16,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 16,03</t>
+          <t>4,26; 16,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,42</t>
+          <t>-1,43; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 108,3</t>
+          <t>-42,45; 104,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,07; 244,93</t>
+          <t>44,81; 246,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,37; 233,34</t>
+          <t>35,65; 235,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 391,3</t>
+          <t>-51,69; 348,12</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,32</t>
+          <t>3,39; 11,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,97</t>
+          <t>2,64; 11,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,24</t>
+          <t>2,75; 8,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,04</t>
+          <t>0,12; 6,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,5; 206,53</t>
+          <t>34,91; 207,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,49; 184,39</t>
+          <t>25,04; 193,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,94; 473,58</t>
+          <t>65,53; 514,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 132,65</t>
+          <t>1,14; 131,61</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,98</t>
+          <t>0,1; 4,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 9,95</t>
+          <t>1,38; 9,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,77</t>
+          <t>0,32; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,62</t>
+          <t>-2,18; 3,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 1316,77</t>
+          <t>-29,36; 1214,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,63; 265,76</t>
+          <t>18,19; 265,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 490,23</t>
+          <t>-3,42; 610,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 86,31</t>
+          <t>-28,98; 103,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,68</t>
+          <t>2,4; 8,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,91; 19,23</t>
+          <t>9,75; 19,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 14,95</t>
+          <t>5,08; 15,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 7,41</t>
+          <t>-1,84; 7,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,13; 998,25</t>
+          <t>61,98; 951,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>114,27; 422,15</t>
+          <t>119,56; 451,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,51; 221,06</t>
+          <t>44,4; 221,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 171,58</t>
+          <t>-21,98; 208,27</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,48</t>
+          <t>-4,97; 4,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 19,51</t>
+          <t>7,43; 19,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 8,62</t>
+          <t>-0,62; 8,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,72</t>
+          <t>2,53; 9,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 116,71</t>
+          <t>-60,39; 113,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>105,39; 848,34</t>
+          <t>95,47; 753,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 354,04</t>
+          <t>-16,46; 401,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,46; 528,61</t>
+          <t>47,3; 515,32</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,24</t>
+          <t>0,16; 5,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 7,9</t>
+          <t>-0,88; 8,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,69</t>
+          <t>-0,08; 10,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 4,82</t>
+          <t>-1,47; 4,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 893,08</t>
+          <t>-29,61; 1056,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 155,16</t>
+          <t>-10,85; 175,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 158,77</t>
+          <t>-3,22; 183,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 130,11</t>
+          <t>-22,62; 130,72</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,42</t>
+          <t>1,33; 7,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,96</t>
+          <t>0,64; 5,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,37</t>
+          <t>2,52; 9,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 6,17</t>
+          <t>-4,95; 6,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,66; 190,16</t>
+          <t>18,24; 179,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,43; 193,2</t>
+          <t>10,79; 190,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,77; 204,89</t>
+          <t>33,94; 202,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 84,95</t>
+          <t>-44,41; 93,74</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,36</t>
+          <t>-1,04; 4,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,92</t>
+          <t>3,46; 10,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,13</t>
+          <t>0,48; 5,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,24; 15,39</t>
+          <t>8,42; 15,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 71,39</t>
+          <t>-12,49; 73,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,35; 143,72</t>
+          <t>31,88; 149,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,76; 161,31</t>
+          <t>7,64; 157,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>133,63; 719,83</t>
+          <t>140,98; 640,34</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,54</t>
+          <t>2,05; 4,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,68</t>
+          <t>5,79; 8,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,57</t>
+          <t>4,07; 6,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,18</t>
+          <t>2,68; 6,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,16; 97,34</t>
+          <t>35,16; 96,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74,5; 140,91</t>
+          <t>79,72; 146,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,92; 137,83</t>
+          <t>69,26; 140,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46,94; 135,45</t>
+          <t>45,71; 133,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1002-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 5,1</t>
+          <t>-4,14; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 16,72</t>
+          <t>4,96; 16,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 16,26</t>
+          <t>4,85; 16,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,26</t>
+          <t>-0,91; 2,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 104,61</t>
+          <t>-43,55; 103,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,81; 246,92</t>
+          <t>41,79; 253,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,65; 235,79</t>
+          <t>36,24; 238,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,69; 348,12</t>
+          <t>-36,73; 389,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>50,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,06</t>
+          <t>3,46; 11,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,04</t>
+          <t>2,56; 11,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,47</t>
+          <t>2,47; 8,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 6,76</t>
+          <t>0,21; 6,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,91; 207,94</t>
+          <t>35,99; 198,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,04; 193,94</t>
+          <t>24,18; 200,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,53; 514,81</t>
+          <t>60,76; 501,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 131,61</t>
+          <t>0,53; 127,86</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,58</t>
+          <t>0,03; 4,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,92</t>
+          <t>1,28; 10,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 6,29</t>
+          <t>0,16; 6,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,91</t>
+          <t>-2,72; 3,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 1214,21</t>
+          <t>-23,96; 1261,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 265,46</t>
+          <t>9,13; 286,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 610,63</t>
+          <t>-10,52; 592,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 103,43</t>
+          <t>-35,13; 85,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>101,66%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,18</t>
+          <t>2,38; 8,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 19,2</t>
+          <t>9,36; 19,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,29</t>
+          <t>5,28; 14,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 7,88</t>
+          <t>1,75; 9,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,98; 951,37</t>
+          <t>58,21; 1284,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>119,56; 451,29</t>
+          <t>110,22; 418,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,4; 221,1</t>
+          <t>43,54; 222,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 208,27</t>
+          <t>19,55; 267,18</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>189,76%</t>
+          <t>193,79%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,05</t>
+          <t>-4,79; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 19,19</t>
+          <t>7,25; 19,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 8,44</t>
+          <t>-0,79; 8,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 9,18</t>
+          <t>2,5; 8,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 113,94</t>
+          <t>-55,56; 124,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,47; 753,8</t>
+          <t>104,59; 757,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 401,51</t>
+          <t>-14,55; 357,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,3; 515,32</t>
+          <t>55,99; 530,41</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,44</t>
+          <t>0,11; 5,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,35</t>
+          <t>-1,43; 7,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 10,33</t>
+          <t>-1,19; 9,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,87</t>
+          <t>-1,04; 5,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 1056,68</t>
+          <t>-28,62; 1241,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 175,47</t>
+          <t>-15,13; 160,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 183,01</t>
+          <t>-12,53; 176,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 130,72</t>
+          <t>-14,95; 151,57</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,19</t>
+          <t>1,36; 7,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,89</t>
+          <t>0,6; 6,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,1</t>
+          <t>2,64; 9,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 6,4</t>
+          <t>2,48; 8,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,24; 179,26</t>
+          <t>16,72; 181,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 190,43</t>
+          <t>9,51; 192,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,94; 202,94</t>
+          <t>33,48; 200,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-44,41; 93,74</t>
+          <t>25,42; 146,46</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>9,21</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>265,68%</t>
+          <t>161,54%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,43</t>
+          <t>-1,07; 4,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,46</t>
+          <t>3,46; 10,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,13</t>
+          <t>0,43; 5,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,42; 15,03</t>
+          <t>6,73; 11,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 73,55</t>
+          <t>-12,09; 73,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,88; 149,95</t>
+          <t>32,4; 144,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,64; 157,55</t>
+          <t>8,0; 162,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>140,98; 640,34</t>
+          <t>94,41; 260,04</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,54</t>
+          <t>2,06; 4,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,85</t>
+          <t>5,72; 8,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,64</t>
+          <t>3,99; 6,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,18</t>
+          <t>3,93; 6,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,16; 96,6</t>
+          <t>34,81; 97,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79,72; 146,27</t>
+          <t>76,37; 141,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,26; 140,87</t>
+          <t>69,32; 141,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>45,71; 133,57</t>
+          <t>60,2; 119,47</t>
         </is>
       </c>
     </row>
